--- a/pre-week-2/Homework2.xlsx
+++ b/pre-week-2/Homework2.xlsx
@@ -8,14 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimmy\OneDrive\Desktop\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E464C23-1776-4E93-B244-2668B500EC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E083A7A6-3DD4-4BE3-AEC4-47915734C8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="11956" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="11956" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pivot_Table_Region" sheetId="2" r:id="rId1"/>
+    <sheet name="Store_Region_Summary" sheetId="3" r:id="rId2"/>
+    <sheet name="Pivot_Table_Category" sheetId="5" r:id="rId3"/>
+    <sheet name="Store_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Store_Category_Summary" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="6" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Store</t>
   </si>
@@ -67,6 +74,29 @@
   </si>
   <si>
     <t>Home Goods</t>
+  </si>
+  <si>
+    <t>Numerical Column</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Monthly Sales</t>
+  </si>
+  <si>
+    <t>The West region contributes the most to total monthly sales with $167, followed by the East region ($145). The South and North regions have very similar totals at $143 and $138 respectively. Store H in the West region has a very high monthly sales of 72, which is significantly higher than any other store. This one strong-performing store is clearly influencing and boosting the total sales for the West region. Overall, while sales are fairly balanced across regions, the West region stands out largely due to the outstanding performance of Store H.</t>
+  </si>
+  <si>
+    <t>Electronics is the best-performing category with total monthly sales of $218, followed by Apparel ($195) and Home Goods ($180).
+I selected a Column Chart because it allows for easy visual comparison of the sales totals across the three categories by showing clear differences in bar heights.
+The chart clearly shows that Electronics outperforms the other two categories by a noticeable margin. This insight suggests that the merchandising team should focus more resources and inventory on Electronics products to maximize overall sales.</t>
   </si>
 </sst>
 </file>
@@ -102,8 +132,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -119,6 +158,2354 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Homework2.xlsx]Pivot_Table_Region!PivotTable1</c:name>
+    <c:fmtId val="7"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Total</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Monthly Sales By Region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot_Table_Region!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot_Table_Region!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot_Table_Region!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>167</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2968-4EEC-90D6-AF926D16F1FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Homework2.xlsx]Pivot_Table_Category!PivotTable3</c:name>
+    <c:fmtId val="16"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Total</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Monthly Sales by Category</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pivot_Table_Category!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pivot_Table_Category!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Apparel</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electrionics</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Home Goods</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pivot_Table_Category!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5FB4-49B3-A7D2-9BFA9AFDC7D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="64306895"/>
+        <c:axId val="64308815"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="64306895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="64308815"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="64308815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="64306895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>626268</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>16668</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>52388</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C45DFA9-6CBB-319F-0439-022AC65B020F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>78580</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>116680</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{491DC5C0-7877-34E1-A074-1469DF722299}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jimmy Juarez" refreshedDate="46112.052650694444" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{36CF15A8-ECB9-4F36-95DB-EF9959E564D8}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D13" sheet="Store_Data"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Store" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="West"/>
+        <s v="East"/>
+        <s v="North"/>
+        <s v="South"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Electrionics"/>
+        <s v="Apparel"/>
+        <s v="Home Goods"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Monthly Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="43" maxValue="72"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <s v="Store A"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="72"/>
+  </r>
+  <r>
+    <s v="Store B"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="52"/>
+  </r>
+  <r>
+    <s v="Store C"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="51"/>
+  </r>
+  <r>
+    <s v="Store D"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <s v="Store E"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="49"/>
+  </r>
+  <r>
+    <s v="Store F"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="48"/>
+  </r>
+  <r>
+    <s v="Store G"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="47"/>
+  </r>
+  <r>
+    <s v="Store H"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <s v="Store I"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <s v="Store J"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <s v="Store K"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="44"/>
+  </r>
+  <r>
+    <s v="Store L"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="43"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65355C03-93CA-4133-B12E-E1C9FF186797}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly Sales" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="7" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30C954FE-147A-49D2-8957-3E359D29DB14}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly Sales" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="16" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A29158CB-5A66-445A-9CF8-03E6EBF29BD5}" name="Table1" displayName="Table1" ref="H2:I5" totalsRowShown="0">
+  <autoFilter ref="H2:I5" xr:uid="{A29158CB-5A66-445A-9CF8-03E6EBF29BD5}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C748A345-301C-4048-B59B-5DA993E4E7F6}" name="Numerical Column"/>
+    <tableColumn id="2" xr3:uid="{7AD08645-A956-49A1-956B-8C4D893EFBCF}" name="Column2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -383,15 +2770,153 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AF13A8-2532-48ED-9D5C-C775FA0B9520}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4">
+        <v>593</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83ECD8B3-A9AF-4B93-9ADE-75608B9FCF74}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="70.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF8F574-9E49-4EAC-A750-E6F6D75D9560}">
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>593</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.06640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -405,184 +2930,226 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <f>"Store " &amp; CHAR(64 + ROW(A2) - 1)</f>
         <v>Store A</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>51</v>
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
-        <f t="shared" ref="A3:A13" si="0">"Store " &amp; CHAR(64 + ROW(A3) - 1)</f>
+        <f>"Store " &amp; CHAR(64 + ROW(A3) - 1)</f>
         <v>Store B</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
-        <f t="shared" si="0"/>
+        <f>"Store " &amp; CHAR(64 + ROW(A4) - 1)</f>
         <v>Store C</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4">
+        <v>51</v>
+      </c>
+      <c r="I4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="str">
+        <f>"Store " &amp; CHAR(64 + ROW(A5) - 1)</f>
+        <v>Store D</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="str">
+        <f>"Store " &amp; CHAR(64 + ROW(A6) - 1)</f>
+        <v>Store E</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
-        <f t="shared" si="0"/>
-        <v>Store D</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="str">
+        <f>"Store " &amp; CHAR(64 + ROW(A7) - 1)</f>
+        <v>Store F</v>
+      </c>
+      <c r="B7" t="s">
         <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
-        <f t="shared" si="0"/>
-        <v>Store E</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
-        <f t="shared" si="0"/>
-        <v>Store F</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="str">
+        <f>"Store " &amp; CHAR(64 + ROW(A8) - 1)</f>
+        <v>Store G</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
-        <f t="shared" si="0"/>
-        <v>Store G</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="str">
+        <f>"Store " &amp; CHAR(64 + ROW(A9) - 1)</f>
+        <v>Store H</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="D8">
-        <v>45</v>
+      <c r="D9">
+        <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="str">
-        <f t="shared" si="0"/>
-        <v>Store H</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <f>"Store " &amp; CHAR(64 + ROW(A10) - 1)</f>
         <v>Store I</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
-        <f t="shared" si="0"/>
+        <f>"Store " &amp; CHAR(64 + ROW(A11) - 1)</f>
         <v>Store J</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="str">
         <f>"Store " &amp; CHAR(64 + ROW(A12) - 1)</f>
         <v>Store K</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="str">
+        <f>"Store " &amp; CHAR(64 + ROW(A13) - 1)</f>
+        <v>Store L</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D12">
-        <v>46</v>
+      <c r="D13">
+        <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" t="str">
-        <f t="shared" si="0"/>
-        <v>Store L</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D13">
+    <sortCondition descending="1" ref="D2:D13"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D5B476-7797-4C95-93FE-78CE72369759}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="61.06640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="128.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
